--- a/artfynd/A 25192-2026 artfynd.xlsx
+++ b/artfynd/A 25192-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134638372</v>
+        <v>134745133</v>
       </c>
       <c r="B2" t="n">
-        <v>99112</v>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>gebo, Sm</t>
+          <t>Gebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547602</v>
+        <v>547693</v>
       </c>
       <c r="R2" t="n">
-        <v>6390778</v>
+        <v>6390802</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +751,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,50 +794,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134638373</v>
+        <v>134745278</v>
       </c>
       <c r="B3" t="n">
-        <v>99112</v>
+        <v>58260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -850,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547599</v>
+        <v>547735</v>
       </c>
       <c r="R3" t="n">
-        <v>6390787</v>
+        <v>6390822</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,22 +867,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>08:57</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>08:57</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -923,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134638374</v>
+        <v>134638372</v>
       </c>
       <c r="B4" t="n">
-        <v>98060</v>
+        <v>99112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,31 +910,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -970,14 +946,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gebo, Sm</t>
+          <t>gebo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547734</v>
+        <v>547602</v>
       </c>
       <c r="R4" t="n">
-        <v>6390794</v>
+        <v>6390778</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134638375</v>
+        <v>134638373</v>
       </c>
       <c r="B5" t="n">
-        <v>98060</v>
+        <v>99112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,26 +1034,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1086,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547715</v>
+        <v>547599</v>
       </c>
       <c r="R5" t="n">
-        <v>6390815</v>
+        <v>6390787</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,6 +1144,1330 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134745127</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>547616</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6390768</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134745128</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>547574</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6390777</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134745125</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>547783</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6390816</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134745126</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>547669</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6390768</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134745129</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>547655</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6390786</v>
+      </c>
+      <c r="S10" t="n">
+        <v>12</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134745130</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>547664</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6390792</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134745131</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>547685</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6390801</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134745132</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>547697</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6390774</v>
+      </c>
+      <c r="S13" t="n">
+        <v>13</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134745134</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>547653</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6390825</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134638374</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>547734</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6390794</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134638375</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>547715</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6390815</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25192-2026 artfynd.xlsx
+++ b/artfynd/A 25192-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745133</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745278</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134638372</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134638373</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1264,6 +1289,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745127</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1388,6 +1418,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745128</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1508,6 +1543,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745125</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1628,6 +1668,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745126</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1752,6 +1797,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745129</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1872,6 +1922,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745130</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1992,6 +2047,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745131</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2112,6 +2172,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745132</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2232,6 +2297,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745134</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2356,6 +2426,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134638374</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2468,8 +2543,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134638375</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>